--- a/artfynd/S 667-2021 artfynd.xlsx
+++ b/artfynd/S 667-2021 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98737094</v>
+        <v>135431197</v>
       </c>
       <c r="B3" t="n">
-        <v>79746</v>
+        <v>79860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>6639173</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,17 +869,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-02-20</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-02-20</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt på barken av stor, levande skogsalm</t>
+          <t>Almen är, efter en oundviklig död, nedsågad och bortforslag. Kvar står en högstubbe där barken håller på att falla av. Savlundlaven sjunger på den sista versen. Det var fint så länge det varade.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,11 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,24 +904,24 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Bark på högstubbe # Ulmus glabra</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Rasmus Elleby, Samuel Persson, Jon Jörpeland</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98737094</t>
+          <t>https://artportalen.se/Sighting/135431197</t>
         </is>
       </c>
     </row>

--- a/artfynd/S 667-2021 artfynd.xlsx
+++ b/artfynd/S 667-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135431197</v>
       </c>
       <c r="B3" t="n">
-        <v>79860</v>
+        <v>79862</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 667-2021 artfynd.xlsx
+++ b/artfynd/S 667-2021 artfynd.xlsx
@@ -15930,10 +15930,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>69546925</v>
+        <v>104191000</v>
       </c>
       <c r="B132" t="n">
-        <v>88345</v>
+        <v>89206</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15941,26 +15941,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4566</v>
+        <v>4393</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dofttråding</t>
+          <t>Papegojvaxing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Inosperma bongardii</t>
+          <t>Gliophorus psittacinus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Weinm.) Matheny &amp; Estev-Rav.</t>
+          <t>(Schaeff.) Herink</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -15968,19 +15968,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Hallkved 1 km NO om Funbo kyrka, Upl</t>
+          <t>Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>660785</v>
+        <v>660732</v>
       </c>
       <c r="R132" t="n">
-        <v>6639043</v>
+        <v>6639094</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16004,17 +16006,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2001-09-19</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2001-09-19</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Ca. 10 ex. på bar jord under hassel.</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16023,33 +16020,34 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Samuel Persson, Margaux Boeraeve</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69546925</t>
+          <t>https://artportalen.se/Sighting/104191000</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1367497</v>
+        <v>69546925</v>
       </c>
       <c r="B133" t="n">
-        <v>91087</v>
+        <v>88345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16057,34 +16055,43 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4823</v>
+        <v>4566</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Hasselsopp</t>
+          <t>Dofttråding</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Leccinellum pseudoscabrum</t>
+          <t>Inosperma bongardii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Kallenb.) Mikšík</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(Weinm.) Matheny &amp; Estev-Rav.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Hallkved, mellan herrgården och riksvägen, Upl</t>
+          <t>Hallkved 1 km NO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>660830</v>
+        <v>660785</v>
       </c>
       <c r="R133" t="n">
-        <v>6638949</v>
+        <v>6639043</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16111,12 +16118,17 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2012-08-17</t>
+          <t>2001-09-19</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2012-08-17</t>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Ca. 10 ex. på bar jord under hassel.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16127,33 +16139,28 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>Ädellövskog med ek, lind, asp, hassel mm</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1367497</t>
+          <t>https://artportalen.se/Sighting/69546925</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>16505954</v>
+        <v>1367497</v>
       </c>
       <c r="B134" t="n">
         <v>91087</v>
@@ -16181,26 +16188,17 @@
           <t>(Kallenb.) Mikšík</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Hallkved 1 km NO om Funbo kyrka, Upl</t>
+          <t>Hallkved, mellan herrgården och riksvägen, Upl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>660850</v>
+        <v>660830</v>
       </c>
       <c r="R134" t="n">
-        <v>6638913</v>
+        <v>6638949</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16227,17 +16225,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
+          <t>2012-08-17</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2012-07-17</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>1 ex. under ek och hassel.</t>
+          <t>2012-08-17</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16251,71 +16244,77 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Äldre lövskog.</t>
+          <t>Ädellövskog med ek, lind, asp, hassel mm</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16505954</t>
+          <t>https://artportalen.se/Sighting/1367497</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>106228544</v>
+        <v>16505954</v>
       </c>
       <c r="B135" t="n">
-        <v>91867</v>
+        <v>91087</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5445</v>
+        <v>4823</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Hasselsopp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Leccinellum pseudoscabrum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+          <t>(Kallenb.) Mikšík</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Hallkved, Upl</t>
+          <t>Hallkved 1 km NO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>660856</v>
+        <v>660850</v>
       </c>
       <c r="R135" t="n">
-        <v>6639137</v>
+        <v>6638913</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16342,12 +16341,17 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2012-07-17</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2012-07-17</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>1 ex. under ek och hassel.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16356,82 +16360,79 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>Äldre lövskog.</t>
+        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106228544</t>
+          <t>https://artportalen.se/Sighting/16505954</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>112103096</v>
+        <v>106228544</v>
       </c>
       <c r="B136" t="n">
-        <v>91683</v>
+        <v>91867</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5678</v>
+        <v>5445</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kruskantarell</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Craterellus undulatus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) E.Campo &amp; Papetti</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Hallkved, Hallkved, Upl</t>
+          <t>Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>660822</v>
+        <v>660856</v>
       </c>
       <c r="R136" t="n">
-        <v>6639190</v>
+        <v>6639137</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16455,22 +16456,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2023-01-28</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2023-01-28</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16479,30 +16470,31 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Magnus Friberg</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Magnus Friberg</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112103096</t>
+          <t>https://artportalen.se/Sighting/106228544</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>112111855</v>
+        <v>112103096</v>
       </c>
       <c r="B137" t="n">
         <v>91683</v>
@@ -16530,23 +16522,30 @@
           <t>(Fr.) E.Campo &amp; Papetti</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Hallkved, Upl</t>
+          <t>Hallkved, Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>660829</v>
+        <v>660822</v>
       </c>
       <c r="R137" t="n">
-        <v>6639186</v>
+        <v>6639190</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16575,7 +16574,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16585,7 +16584,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16594,31 +16593,30 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Magnus Friberg</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Rasmus Elleby, Magnus Friberg</t>
+          <t>Magnus Friberg</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112111855</t>
+          <t>https://artportalen.se/Sighting/112103096</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>112189470</v>
+        <v>112111855</v>
       </c>
       <c r="B138" t="n">
         <v>91683</v>
@@ -16656,10 +16654,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>660823</v>
+        <v>660829</v>
       </c>
       <c r="R138" t="n">
-        <v>6639190</v>
+        <v>6639186</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16686,17 +16684,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Återfynd.</t>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16712,27 +16715,27 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Gunnar Siljestrand</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Gunnar Siljestrand, Birgitta Davidsson</t>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Rasmus Elleby, Magnus Friberg</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112189470</t>
+          <t>https://artportalen.se/Sighting/112111855</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>75093051</v>
+        <v>112189470</v>
       </c>
       <c r="B139" t="n">
-        <v>92928</v>
+        <v>91683</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16740,43 +16743,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5836</v>
+        <v>5678</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Kruskantarell</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Craterellus undulatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Campo &amp; Papetti</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Hallkved 1 km NO om Funbo kyrka, Upl</t>
+          <t>Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>660737</v>
+        <v>660823</v>
       </c>
       <c r="R139" t="n">
-        <v>6638983</v>
+        <v>6639190</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16803,17 +16800,17 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2001-09-06</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2001-09-06</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>1 ex. under lind, asp och hassel.</t>
+          <t>Återfynd.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16822,33 +16819,34 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Gunnar Siljestrand</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Gunnar Siljestrand, Birgitta Davidsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75093051</t>
+          <t>https://artportalen.se/Sighting/112189470</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>98699114</v>
+        <v>75093051</v>
       </c>
       <c r="B140" t="n">
-        <v>79707</v>
+        <v>92928</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16856,37 +16854,43 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6431</v>
+        <v>5836</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Hallkved, Upl</t>
+          <t>Hallkved 1 km NO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>660651</v>
+        <v>660737</v>
       </c>
       <c r="R140" t="n">
-        <v>6639185</v>
+        <v>6638983</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16913,12 +16917,17 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2022-02-20</t>
+          <t>2001-09-06</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2022-02-20</t>
+          <t>2001-09-06</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>1 ex. under lind, asp och hassel.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16927,54 +16936,33 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Samuel Persson, Jon Jörpeland, Karl Soler Kinnerbäck, Rasmus Elleby</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98699114</t>
+          <t>https://artportalen.se/Sighting/75093051</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>98699263</v>
+        <v>98699114</v>
       </c>
       <c r="B141" t="n">
-        <v>78753</v>
+        <v>79707</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16982,21 +16970,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6435</v>
+        <v>6431</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vitskivlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Diplotomma alboatrum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hoffm.) Flot.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -17091,13 +17079,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98699263</t>
+          <t>https://artportalen.se/Sighting/98699114</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>114335451</v>
+        <v>98699263</v>
       </c>
       <c r="B142" t="n">
         <v>78753</v>
@@ -17126,19 +17114,22 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Syd Hallkved, Funbosjön, Upl</t>
+          <t>Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>660659</v>
+        <v>660651</v>
       </c>
       <c r="R142" t="n">
-        <v>6639169</v>
+        <v>6639185</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -17162,17 +17153,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Längre allé mellan landsvägen och Hallkved, på alm</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17185,27 +17171,47 @@
       <c r="AG142" t="b">
         <v>0</v>
       </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Ulmus glabra</t>
+        </is>
+      </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Svante Hultengren</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Svante Hultengren</t>
+          <t>Samuel Persson, Jon Jörpeland, Karl Soler Kinnerbäck, Rasmus Elleby</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114335451</t>
+          <t>https://artportalen.se/Sighting/98699263</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130364301</v>
+        <v>114335451</v>
       </c>
       <c r="B143" t="n">
         <v>78753</v>
@@ -17236,14 +17242,14 @@
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Hallkved, NO om Funbo kyrka, Upl</t>
+          <t>Syd Hallkved, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>660655</v>
+        <v>660659</v>
       </c>
       <c r="R143" t="n">
-        <v>6639172</v>
+        <v>6639169</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -17270,17 +17276,17 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>På bark på död, stående alm (almsjukedödat träd), omkr. 340 cm.</t>
+          <t>Längre allé mellan landsvägen och Hallkved, på alm</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17289,53 +17295,34 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>Gammal allé.</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>Bark på död, stående alm (almsjukedödat träd), omkr. 340 cm. # Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Svante Hultengren</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Svante Hultengren</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130364301</t>
+          <t>https://artportalen.se/Sighting/114335451</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>114335460</v>
+        <v>130364301</v>
       </c>
       <c r="B144" t="n">
-        <v>78728</v>
+        <v>78753</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17343,37 +17330,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6436</v>
+        <v>6435</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Vitskivlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Diplotomma alboatrum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Hoffm.) Flot.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Syd Hallkved, Funbosjön, Upl</t>
+          <t>Hallkved, NO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>660899</v>
+        <v>660655</v>
       </c>
       <c r="R144" t="n">
-        <v>6639000</v>
+        <v>6639172</v>
       </c>
       <c r="S144" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -17397,17 +17384,17 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Betad hagmark med inslag av grov ek och lind, på ek</t>
+          <t>På bark på död, stående alm (almsjukedödat träd), omkr. 340 cm.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17418,31 +17405,51 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>Gammal allé.</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Bark på död, stående alm (almsjukedödat träd), omkr. 340 cm. # Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Svante Hultengren</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Svante Hultengren</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114335460</t>
+          <t>https://artportalen.se/Sighting/130364301</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>114335458</v>
+        <v>114335460</v>
       </c>
       <c r="B145" t="n">
-        <v>83290</v>
+        <v>78728</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17450,21 +17457,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6439</v>
+        <v>6436</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -17474,13 +17481,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>660659</v>
+        <v>660899</v>
       </c>
       <c r="R145" t="n">
-        <v>6639169</v>
+        <v>6639000</v>
       </c>
       <c r="S145" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17514,7 +17521,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Längre allé mellan landsvägen och Hallkved, på alm</t>
+          <t>Betad hagmark med inslag av grov ek och lind, på ek</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17540,13 +17547,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114335458</t>
+          <t>https://artportalen.se/Sighting/114335460</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130364306</v>
+        <v>114335458</v>
       </c>
       <c r="B146" t="n">
         <v>83290</v>
@@ -17577,14 +17584,14 @@
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Hallkved, NO om Funbo kyrka, Upl</t>
+          <t>Syd Hallkved, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>660655</v>
+        <v>660659</v>
       </c>
       <c r="R146" t="n">
-        <v>6639172</v>
+        <v>6639169</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -17611,17 +17618,17 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>På bark på död, stående alm (almsjukedödat träd), omkr. 340 cm.</t>
+          <t>Längre allé mellan landsvägen och Hallkved, på alm</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17632,89 +17639,69 @@
       </c>
       <c r="AG146" t="b">
         <v>0</v>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>Gammal allé.</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>Bark på död, stående alm (almsjukedödat träd), omkr. 340 cm. # Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Svante Hultengren</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Svante Hultengren</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130364306</t>
+          <t>https://artportalen.se/Sighting/114335458</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>6927034</v>
+        <v>130364306</v>
       </c>
       <c r="B147" t="n">
-        <v>80432</v>
+        <v>83290</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Halkved S-ut, Upl</t>
+          <t>Hallkved, NO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>660766</v>
+        <v>660655</v>
       </c>
       <c r="R147" t="n">
-        <v>6639310</v>
+        <v>6639172</v>
       </c>
       <c r="S147" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -17738,12 +17725,17 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2013-09-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2013-09-01</t>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>På bark på död, stående alm (almsjukedödat träd), omkr. 340 cm.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17754,28 +17746,48 @@
       </c>
       <c r="AG147" t="b">
         <v>0</v>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>Gammal allé.</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Bark på död, stående alm (almsjukedödat träd), omkr. 340 cm. # Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6927034</t>
+          <t>https://artportalen.se/Sighting/130364306</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>93014852</v>
+        <v>6927034</v>
       </c>
       <c r="B148" t="n">
         <v>80432</v>
@@ -17804,22 +17816,19 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Hallkved, Upl</t>
+          <t>Halkved S-ut, Upl</t>
         </is>
       </c>
       <c r="Q148" t="n">
         <v>660766</v>
       </c>
       <c r="R148" t="n">
-        <v>6639318</v>
+        <v>6639310</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17843,12 +17852,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2021-05-02</t>
+          <t>2013-09-01</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2021-05-02</t>
+          <t>2013-09-01</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17857,46 +17866,30 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93014852</t>
+          <t>https://artportalen.se/Sighting/6927034</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>109262546</v>
+        <v>93014852</v>
       </c>
       <c r="B149" t="n">
         <v>80432</v>
@@ -17925,20 +17918,22 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>660920</v>
+        <v>660766</v>
       </c>
       <c r="R149" t="n">
-        <v>6639184</v>
+        <v>6639318</v>
       </c>
       <c r="S149" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17962,12 +17957,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2021-05-02</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2021-05-02</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17976,8 +17971,24 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
@@ -17993,13 +18004,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109262546</t>
+          <t>https://artportalen.se/Sighting/93014852</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>112111230</v>
+        <v>109262546</v>
       </c>
       <c r="B150" t="n">
         <v>80432</v>
@@ -18028,19 +18039,17 @@
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>660767</v>
+        <v>660920</v>
       </c>
       <c r="R150" t="n">
-        <v>6639309</v>
+        <v>6639184</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -18067,22 +18076,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18091,31 +18090,30 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Rasmus Elleby</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112111230</t>
+          <t>https://artportalen.se/Sighting/109262546</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>114335448</v>
+        <v>112111230</v>
       </c>
       <c r="B151" t="n">
         <v>80432</v>
@@ -18144,19 +18142,22 @@
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Syd Hallkved, Funbosjön, Upl</t>
+          <t>Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>660771</v>
+        <v>660767</v>
       </c>
       <c r="R151" t="n">
-        <v>6639316</v>
+        <v>6639309</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -18180,17 +18181,22 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Allé mot gården Hallkved, på lönn</t>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18199,55 +18205,56 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Svante Hultengren</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Svante Hultengren</t>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Rasmus Elleby</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114335448</t>
+          <t>https://artportalen.se/Sighting/112111230</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>114335446</v>
+        <v>114335448</v>
       </c>
       <c r="B152" t="n">
-        <v>83314</v>
+        <v>80432</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6471</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18323,54 +18330,54 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114335446</t>
+          <t>https://artportalen.se/Sighting/114335448</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>63205820</v>
+        <v>114335446</v>
       </c>
       <c r="B153" t="n">
-        <v>57247</v>
+        <v>83314</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100038</v>
+        <v>6471</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>S Hallkved, Upl</t>
+          <t>Syd Hallkved, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>660773</v>
+        <v>660771</v>
       </c>
       <c r="R153" t="n">
-        <v>6639047</v>
+        <v>6639316</v>
       </c>
       <c r="S153" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -18394,17 +18401,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>S Hallkved</t>
+          <t>Allé mot gården Hallkved, på lönn</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18419,27 +18426,27 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Per Stolpe</t>
+          <t>Svante Hultengren</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Pär Eriksson</t>
+          <t>Svante Hultengren</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63205820</t>
+          <t>https://artportalen.se/Sighting/114335446</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>117454870</v>
+        <v>63205820</v>
       </c>
       <c r="B154" t="n">
-        <v>58435</v>
+        <v>57247</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18447,46 +18454,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100058</v>
+        <v>100038</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mindre flugsnappare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ficedula parva</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Bechstein, 1794)</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Södra lunden, Funbo, Funbosjön, Upl</t>
+          <t>S Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>660751</v>
+        <v>660773</v>
       </c>
       <c r="R154" t="n">
-        <v>6639029</v>
+        <v>6639047</v>
       </c>
       <c r="S154" t="n">
         <v>100</v>
@@ -18513,22 +18508,17 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>08:40</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2002-01-01</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>S Hallkved</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18543,49 +18533,49 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Ragnar Hall</t>
+          <t>Per Stolpe</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Ragnar Hall</t>
+          <t>Pär Eriksson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117454870</t>
+          <t>https://artportalen.se/Sighting/63205820</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124514657</v>
+        <v>117454870</v>
       </c>
       <c r="B155" t="n">
-        <v>6675</v>
+        <v>58435</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100763</v>
+        <v>100058</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Mindre flugsnappare</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Ficedula parva</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Bechstein, 1794)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -18593,28 +18583,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Hallkved, Funbo, Upl</t>
+          <t>Södra lunden, Funbo, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>660802</v>
+        <v>660751</v>
       </c>
       <c r="R155" t="n">
-        <v>6638968</v>
+        <v>6639029</v>
       </c>
       <c r="S155" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18638,12 +18627,22 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18652,34 +18651,33 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Johan Carlsson</t>
+          <t>Ragnar Hall</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Johan Carlsson</t>
+          <t>Ragnar Hall</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124514657</t>
+          <t>https://artportalen.se/Sighting/117454870</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132625255</v>
+        <v>124514657</v>
       </c>
       <c r="B156" t="n">
-        <v>6826</v>
+        <v>6675</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18710,31 +18708,27 @@
         </is>
       </c>
       <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Hallkved, Upl</t>
+          <t>Hallkved, Funbo, Upl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>660724</v>
+        <v>660802</v>
       </c>
       <c r="R156" t="n">
-        <v>6639065</v>
+        <v>6638968</v>
       </c>
       <c r="S156" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18758,12 +18752,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18776,67 +18770,52 @@
       <c r="AG156" t="b">
         <v>0</v>
       </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Johan Carlsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Johan Carlsson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132625255</t>
+          <t>https://artportalen.se/Sighting/124514657</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132924101</v>
+        <v>132625255</v>
       </c>
       <c r="B157" t="n">
-        <v>8944</v>
+        <v>6826</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100928</v>
+        <v>100763</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hålskenknäppare</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Eucnemis capucinus</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Ahrens, 1812</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -18844,24 +18823,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Hallkvedsskogen Funbo, Upl</t>
+          <t>Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>660807</v>
+        <v>660724</v>
       </c>
       <c r="R157" t="n">
-        <v>6639159</v>
+        <v>6639065</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18885,12 +18872,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18899,71 +18886,96 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Simon Carrington</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Simon Carrington</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132924101</t>
+          <t>https://artportalen.se/Sighting/132625255</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>63205823</v>
+        <v>132924101</v>
       </c>
       <c r="B158" t="n">
-        <v>6269</v>
+        <v>8944</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>101011</v>
+        <v>100928</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Avlång flatbagge</t>
+          <t>Hålskenknäppare</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Grynocharis oblonga</t>
+          <t>Eucnemis capucinus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>Ahrens, 1812</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>S Hallkved, Upl</t>
+          <t>Hallkvedsskogen Funbo, Upl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>660773</v>
+        <v>660807</v>
       </c>
       <c r="R158" t="n">
-        <v>6639047</v>
+        <v>6639159</v>
       </c>
       <c r="S158" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18987,17 +18999,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>S Hallkved</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19012,27 +19019,27 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Per Stolpe</t>
+          <t>Simon Carrington</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Pär Eriksson</t>
+          <t>Simon Carrington</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63205823</t>
+          <t>https://artportalen.se/Sighting/132924101</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132924064</v>
+        <v>63205823</v>
       </c>
       <c r="B159" t="n">
-        <v>6281</v>
+        <v>6269</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19057,29 +19064,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr">
-        <is>
-          <t>fallfälla</t>
-        </is>
-      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Hallkvedsskogen Funbo, Upl</t>
+          <t>S Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>660807</v>
+        <v>660773</v>
       </c>
       <c r="R159" t="n">
-        <v>6639159</v>
+        <v>6639047</v>
       </c>
       <c r="S159" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -19103,12 +19101,17 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2001-01-01</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>S Hallkved</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19123,49 +19126,49 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Simon Carrington</t>
+          <t>Per Stolpe</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Simon Carrington</t>
+          <t>Pär Eriksson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132924064</t>
+          <t>https://artportalen.se/Sighting/63205823</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132924000</v>
+        <v>132924064</v>
       </c>
       <c r="B160" t="n">
-        <v>12503</v>
+        <v>6281</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>101353</v>
+        <v>101011</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rödhalsad vedsvampbagge</t>
+          <t>Avlång flatbagge</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Mycetophagus fulvicollis</t>
+          <t>Grynocharis oblonga</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Fabricius, 1792</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -19175,7 +19178,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>fönsterfälla</t>
+          <t>fallfälla</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -19214,12 +19217,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19245,16 +19248,16 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132924000</t>
+          <t>https://artportalen.se/Sighting/132924064</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>122318865</v>
+        <v>132924000</v>
       </c>
       <c r="B161" t="n">
-        <v>8436</v>
+        <v>12503</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19262,42 +19265,46 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>101744</v>
+        <v>101353</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Hasselsplintborre</t>
+          <t>Rödhalsad vedsvampbagge</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Scolytus carpini</t>
+          <t>Mycetophagus fulvicollis</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ratzeburg, 1837)</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>Fabricius, 1792</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Södra lunden, Upl</t>
+          <t>Hallkvedsskogen Funbo, Upl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>660905</v>
+        <v>660807</v>
       </c>
       <c r="R161" t="n">
-        <v>6639002</v>
+        <v>6639159</v>
       </c>
       <c r="S161" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -19321,12 +19328,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19337,46 +19344,31 @@
       </c>
       <c r="AG161" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Mats Jonsell</t>
+          <t>Simon Carrington</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Mats Jonsell, Erik Berg</t>
+          <t>Simon Carrington</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122318865</t>
+          <t>https://artportalen.se/Sighting/132924000</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>130550041</v>
+        <v>122318865</v>
       </c>
       <c r="B162" t="n">
-        <v>44149</v>
+        <v>8436</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19384,62 +19376,42 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>102468</v>
+        <v>101744</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Korkmusslingsmal</t>
+          <t>Hasselsplintborre</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Nemapogon fungivorellus</t>
+          <t>Scolytus carpini</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Benander, 1939)</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr"/>
+          <t>(Ratzeburg, 1837)</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>på övervintringsplats</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>insamlad för uppfödning/kläckning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Hallkved, Upl</t>
+          <t>Södra lunden, Upl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>660841</v>
+        <v>660905</v>
       </c>
       <c r="R162" t="n">
-        <v>6639061</v>
+        <v>6639002</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -19471,82 +19443,76 @@
           <t>2025-01-26</t>
         </is>
       </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Kläckt 9 april</t>
-        </is>
-      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>korkmussling</t>
+          <t>hassel</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Fomitopsis quercina</t>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>Fomitopsis quercina</t>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Rasmus Elleby</t>
+          <t>Mats Jonsell</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Rasmus Elleby</t>
+          <t>Mats Jonsell, Erik Berg</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130550041</t>
+          <t>https://artportalen.se/Sighting/122318865</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>117454868</v>
+        <v>130550041</v>
       </c>
       <c r="B163" t="n">
-        <v>58649</v>
+        <v>44149</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>103057</v>
+        <v>102468</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Korkmusslingsmal</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Nemapogon fungivorellus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Benander, 1939)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -19554,27 +19520,40 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr"/>
+          <t>på övervintringsplats</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>insamlad för uppfödning/kläckning</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Södra lunden, Funbo, Funbosjön, Upl</t>
+          <t>Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>660751</v>
+        <v>660841</v>
       </c>
       <c r="R163" t="n">
-        <v>6639029</v>
+        <v>6639061</v>
       </c>
       <c r="S163" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -19598,22 +19577,17 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>08:40</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Kläckt 9 april</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19622,75 +19596,99 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>korkmussling</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Fomitopsis quercina</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>Fomitopsis quercina</t>
+        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Ragnar Hall</t>
+          <t>Rasmus Elleby</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Ragnar Hall</t>
+          <t>Rasmus Elleby</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117454868</t>
+          <t>https://artportalen.se/Sighting/130550041</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125935367</v>
+        <v>117454868</v>
       </c>
       <c r="B164" t="n">
-        <v>108194</v>
+        <v>58649</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220103</v>
+        <v>103057</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Funbo, Upl</t>
+          <t>Södra lunden, Funbo, Funbosjön, Upl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>660809</v>
+        <v>660751</v>
       </c>
       <c r="R164" t="n">
-        <v>6639088</v>
+        <v>6639029</v>
       </c>
       <c r="S164" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -19714,12 +19712,22 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19728,56 +19736,55 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Elias Yngvesson</t>
+          <t>Ragnar Hall</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Elias Yngvesson, Alec Bailey</t>
+          <t>Ragnar Hall</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125935367</t>
+          <t>https://artportalen.se/Sighting/117454868</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>112111156</v>
+        <v>125935367</v>
       </c>
       <c r="B165" t="n">
-        <v>106813</v>
+        <v>108194</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220785</v>
+        <v>220103</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -19787,14 +19794,14 @@
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Hallkved, Upl</t>
+          <t>Funbo, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>660671</v>
+        <v>660809</v>
       </c>
       <c r="R165" t="n">
-        <v>6639229</v>
+        <v>6639088</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -19821,22 +19828,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19852,44 +19849,44 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Elias Yngvesson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Rasmus Elleby</t>
+          <t>Elias Yngvesson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112111156</t>
+          <t>https://artportalen.se/Sighting/125935367</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>112111246</v>
+        <v>112111156</v>
       </c>
       <c r="B166" t="n">
-        <v>106156</v>
+        <v>106813</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -19908,10 +19905,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>660787</v>
+        <v>660671</v>
       </c>
       <c r="R166" t="n">
-        <v>6639278</v>
+        <v>6639229</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -19980,16 +19977,16 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112111246</t>
+          <t>https://artportalen.se/Sighting/112111156</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>4241677</v>
+        <v>112111246</v>
       </c>
       <c r="B167" t="n">
-        <v>103683</v>
+        <v>106156</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19997,16 +19994,16 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>222002</v>
+        <v>221141</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -20015,19 +20012,23 @@
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Hallkved, mellan herrgården och riksvägen, Upl</t>
+          <t>Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>660754</v>
+        <v>660787</v>
       </c>
       <c r="R167" t="n">
-        <v>6639130</v>
+        <v>6639278</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -20051,12 +20052,22 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2012-08-17</t>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2012-08-17</t>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20065,35 +20076,31 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
-      </c>
-      <c r="AI167" t="inlineStr">
-        <is>
-          <t>Ädellövskog med ek, lind, asp, hassel mm</t>
-        </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Rasmus Elleby</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4241677</t>
+          <t>https://artportalen.se/Sighting/112111246</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>112111182</v>
+        <v>4241677</v>
       </c>
       <c r="B168" t="n">
         <v>103683</v>
@@ -20122,23 +20129,19 @@
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Hallkved, Upl</t>
+          <t>Hallkved, mellan herrgården och riksvägen, Upl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>660720</v>
+        <v>660754</v>
       </c>
       <c r="R168" t="n">
-        <v>6639268</v>
+        <v>6639130</v>
       </c>
       <c r="S168" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -20162,22 +20165,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2012-08-17</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2012-08-17</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20186,34 +20179,38 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>Ädellövskog med ek, lind, asp, hassel mm</t>
+        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Rasmus Elleby</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112111182</t>
+          <t>https://artportalen.se/Sighting/4241677</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>92456954</v>
+        <v>112111182</v>
       </c>
       <c r="B169" t="n">
-        <v>104628</v>
+        <v>103683</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20221,16 +20218,16 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>222412</v>
+        <v>222002</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -20238,29 +20235,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>660774</v>
+        <v>660720</v>
       </c>
       <c r="R169" t="n">
-        <v>6639290</v>
+        <v>6639268</v>
       </c>
       <c r="S169" t="n">
         <v>25</v>
@@ -20287,17 +20276,22 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Knoppning och blommade. 70% blommande  45 st plantor totalt</t>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20313,24 +20307,24 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Alice  Hultgren</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Alice  Hultgren</t>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Rasmus Elleby</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92456954</t>
+          <t>https://artportalen.se/Sighting/112111182</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>100228957</v>
+        <v>92456954</v>
       </c>
       <c r="B170" t="n">
         <v>104628</v>
@@ -20358,17 +20352,13 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
       <c r="N170" t="inlineStr">
         <is>
@@ -20377,17 +20367,17 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Hallkved Lundbacken, Funbo, Upl</t>
+          <t>Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>660794</v>
+        <v>660774</v>
       </c>
       <c r="R170" t="n">
-        <v>6639272</v>
+        <v>6639290</v>
       </c>
       <c r="S170" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -20411,17 +20401,17 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Ett större bestånd med ett större antal plantor vid kanten av lundbacken mot åkern på norra sidan. Full blomning.</t>
+          <t>Knoppning och blommade. 70% blommande  45 st plantor totalt</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20437,24 +20427,24 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Johnny Östman</t>
+          <t>Alice  Hultgren</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Johnny Östman</t>
+          <t>Alice  Hultgren</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100228957</t>
+          <t>https://artportalen.se/Sighting/92456954</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>109286682</v>
+        <v>100228957</v>
       </c>
       <c r="B171" t="n">
         <v>104628</v>
@@ -20482,24 +20472,36 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>30</t>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Hallkved, Upl</t>
+          <t>Hallkved Lundbacken, Funbo, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>660792</v>
+        <v>660794</v>
       </c>
       <c r="R171" t="n">
-        <v>6639284</v>
+        <v>6639272</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -20523,12 +20525,17 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2022-04-24</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Ett större bestånd med ett större antal plantor vid kanten av lundbacken mot åkern på norra sidan. Full blomning.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20537,30 +20544,31 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Margaux Boeraeve</t>
+          <t>Johnny Östman</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Margaux Boeraeve, Ward Tamsyn</t>
+          <t>Johnny Östman</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109286682</t>
+          <t>https://artportalen.se/Sighting/100228957</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>112111242</v>
+        <v>109286682</v>
       </c>
       <c r="B172" t="n">
         <v>104628</v>
@@ -20588,28 +20596,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>660787</v>
+        <v>660792</v>
       </c>
       <c r="R172" t="n">
-        <v>6639278</v>
+        <v>6639284</v>
       </c>
       <c r="S172" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -20633,22 +20637,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20657,31 +20651,30 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Margaux Boeraeve</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Rasmus Elleby</t>
+          <t>Margaux Boeraeve, Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112111242</t>
+          <t>https://artportalen.se/Sighting/109286682</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>122796051</v>
+        <v>112111242</v>
       </c>
       <c r="B173" t="n">
         <v>104628</v>
@@ -20709,16 +20702,8 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
           <t>i frukt</t>
@@ -20735,10 +20720,10 @@
         <v>660787</v>
       </c>
       <c r="R173" t="n">
-        <v>6639273</v>
+        <v>6639278</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -20762,22 +20747,22 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20793,27 +20778,27 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Carina Lerdahl</t>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Rasmus Elleby</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122796051</t>
+          <t>https://artportalen.se/Sighting/112111242</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>112111180</v>
+        <v>122796051</v>
       </c>
       <c r="B174" t="n">
-        <v>101326</v>
+        <v>104628</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20821,26 +20806,38 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
@@ -20849,13 +20846,13 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>660720</v>
+        <v>660787</v>
       </c>
       <c r="R174" t="n">
-        <v>6639268</v>
+        <v>6639273</v>
       </c>
       <c r="S174" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -20879,22 +20876,22 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20910,27 +20907,27 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Rasmus Elleby</t>
+          <t>Björn Bråvander, Carina Lerdahl</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112111180</t>
+          <t>https://artportalen.se/Sighting/122796051</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>112111255</v>
+        <v>112111180</v>
       </c>
       <c r="B175" t="n">
-        <v>101228</v>
+        <v>101326</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20938,30 +20935,26 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
@@ -20970,10 +20963,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>660787</v>
+        <v>660720</v>
       </c>
       <c r="R175" t="n">
-        <v>6639278</v>
+        <v>6639268</v>
       </c>
       <c r="S175" t="n">
         <v>25</v>
@@ -21042,62 +21035,62 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112111255</t>
+          <t>https://artportalen.se/Sighting/112111180</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>98731340</v>
+        <v>112111255</v>
       </c>
       <c r="B176" t="n">
-        <v>103403</v>
+        <v>101228</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>223246</v>
+        <v>222771</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Hallkved, 800 m ONO om Funbo kyrka, Upl</t>
+          <t>Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>660653</v>
+        <v>660787</v>
       </c>
       <c r="R176" t="n">
-        <v>6639174</v>
+        <v>6639278</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -21121,17 +21114,22 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2022-02-20</t>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2022-02-20</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Riktigt fint, gammalt träd som såg välmående ut.</t>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -21147,24 +21145,24 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Rasmus Elleby</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Rasmus Elleby, Samuel Persson, Karl Soler Kinnerbäck, Jon Jörpeland</t>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Rasmus Elleby</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98731340</t>
+          <t>https://artportalen.se/Sighting/112111255</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>112112019</v>
+        <v>98731340</v>
       </c>
       <c r="B177" t="n">
         <v>103403</v>
@@ -21192,21 +21190,25 @@
           <t>Huds.</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Hallkved, Upl</t>
+          <t>Hallkved, 800 m ONO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q177" t="n">
         <v>660653</v>
       </c>
       <c r="R177" t="n">
-        <v>6639173</v>
+        <v>6639174</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -21233,22 +21235,17 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2022-02-20</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Riktigt fint, gammalt träd som såg välmående ut.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -21264,62 +21261,66 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Rasmus Elleby</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Rasmus Elleby</t>
+          <t>Rasmus Elleby, Samuel Persson, Karl Soler Kinnerbäck, Jon Jörpeland</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112112019</t>
+          <t>https://artportalen.se/Sighting/98731340</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>59819750</v>
+        <v>112112019</v>
       </c>
       <c r="B178" t="n">
-        <v>89093</v>
+        <v>103403</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>239206</v>
+        <v>223246</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hygrocybe glutinipes var. glutinipes</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Hallkved 1 km NO om Funbo kyrka, Upl</t>
+          <t>Hallkved, Upl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>660623</v>
+        <v>660653</v>
       </c>
       <c r="R178" t="n">
-        <v>6639292</v>
+        <v>6639173</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -21346,17 +21347,22 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2001-09-19</t>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2001-09-19</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Ca. 10 ex. i fuktig betesmark. Hatt upp till 1 cm bred, välvd till utbredd, gul, slemmig, med ixotrichoderm hatthud. Skivor vita till gulvita, vidväxta eller svagt nedlöpande. Fot upp till 1,5 cm hög och 2 mm tjock, gul, slemmig, med ixotrichoderm yta. Sporer 6-8 x 4-5 μm. Celler i lamellköttet &gt; 200 μm långa.</t>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21365,38 +21371,34 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>Naturbetesmark.</t>
-        </is>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Rasmus Elleby</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/59819750</t>
+          <t>https://artportalen.se/Sighting/112112019</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>104191000</v>
+        <v>59819750</v>
       </c>
       <c r="B179" t="n">
-        <v>89060</v>
+        <v>89093</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21404,17 +21406,17 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>239221</v>
+        <v>239206</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus var. psittacinus</t>
+          <t>Hygrocybe glutinipes var. glutinipes</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -21422,21 +21424,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Hallkved, Upl</t>
+          <t>Hallkved 1 km NO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>660732</v>
+        <v>660623</v>
       </c>
       <c r="R179" t="n">
-        <v>6639094</v>
+        <v>6639292</v>
       </c>
       <c r="S179" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -21460,12 +21460,17 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
+          <t>2001-09-19</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Ca. 10 ex. i fuktig betesmark. Hatt upp till 1 cm bred, välvd till utbredd, gul, slemmig, med ixotrichoderm hatthud. Skivor vita till gulvita, vidväxta eller svagt nedlöpande. Fot upp till 1,5 cm hög och 2 mm tjock, gul, slemmig, med ixotrichoderm yta. Sporer 6-8 x 4-5 μm. Celler i lamellköttet &gt; 200 μm långa.</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -21474,25 +21479,29 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
-      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>Naturbetesmark.</t>
+        </is>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Samuel Persson, Margaux Boeraeve</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104191000</t>
+          <t>https://artportalen.se/Sighting/59819750</t>
         </is>
       </c>
     </row>

--- a/artfynd/S 667-2021 artfynd.xlsx
+++ b/artfynd/S 667-2021 artfynd.xlsx
@@ -15933,7 +15933,7 @@
         <v>104191000</v>
       </c>
       <c r="B132" t="n">
-        <v>89206</v>
+        <v>89207</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/S 667-2021 artfynd.xlsx
+++ b/artfynd/S 667-2021 artfynd.xlsx
@@ -15933,7 +15933,7 @@
         <v>104191000</v>
       </c>
       <c r="B132" t="n">
-        <v>89207</v>
+        <v>89213</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/S 667-2021 artfynd.xlsx
+++ b/artfynd/S 667-2021 artfynd.xlsx
@@ -15933,7 +15933,7 @@
         <v>104191000</v>
       </c>
       <c r="B132" t="n">
-        <v>89213</v>
+        <v>89220</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/S 667-2021 artfynd.xlsx
+++ b/artfynd/S 667-2021 artfynd.xlsx
@@ -15933,7 +15933,7 @@
         <v>104191000</v>
       </c>
       <c r="B132" t="n">
-        <v>89220</v>
+        <v>89221</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/S 667-2021 artfynd.xlsx
+++ b/artfynd/S 667-2021 artfynd.xlsx
@@ -15933,7 +15933,7 @@
         <v>104191000</v>
       </c>
       <c r="B132" t="n">
-        <v>89221</v>
+        <v>89234</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/S 667-2021 artfynd.xlsx
+++ b/artfynd/S 667-2021 artfynd.xlsx
@@ -15933,7 +15933,7 @@
         <v>104191000</v>
       </c>
       <c r="B132" t="n">
-        <v>89234</v>
+        <v>89235</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
